--- a/artfynd/A 25919-2025 artfynd.xlsx
+++ b/artfynd/A 25919-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +769,782 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126237645</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100432</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>608781</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7020690</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126237641</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>608525</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7020802</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126237644</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>608781</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7020679</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126237643</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91254</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>608473</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7020757</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126237648</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>608849</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7020693</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126237647</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>608837</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7020681</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126237646</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>608779</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7020711</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126237642</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>608424</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7020779</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25919-2025 artfynd.xlsx
+++ b/artfynd/A 25919-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126222584</v>
       </c>
       <c r="B2" t="n">
-        <v>101429</v>
+        <v>101431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126237645</v>
       </c>
       <c r="B3" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126237641</v>
+        <v>126237643</v>
       </c>
       <c r="B4" t="n">
-        <v>100432</v>
+        <v>91256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608525</v>
+        <v>608473</v>
       </c>
       <c r="R4" t="n">
-        <v>7020802</v>
+        <v>7020757</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126237644</v>
+        <v>126237641</v>
       </c>
       <c r="B5" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608781</v>
+        <v>608525</v>
       </c>
       <c r="R5" t="n">
-        <v>7020679</v>
+        <v>7020802</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126237643</v>
+        <v>126237644</v>
       </c>
       <c r="B6" t="n">
-        <v>91254</v>
+        <v>100434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608473</v>
+        <v>608781</v>
       </c>
       <c r="R6" t="n">
-        <v>7020757</v>
+        <v>7020679</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1163,7 +1163,7 @@
         <v>126237648</v>
       </c>
       <c r="B7" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126237647</v>
       </c>
       <c r="B8" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126237646</v>
       </c>
       <c r="B9" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126237642</v>
       </c>
       <c r="B10" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 25919-2025 artfynd.xlsx
+++ b/artfynd/A 25919-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126222584</v>
       </c>
       <c r="B2" t="n">
-        <v>101431</v>
+        <v>101435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126237645</v>
       </c>
       <c r="B3" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126237643</v>
       </c>
       <c r="B4" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126237641</v>
+        <v>126237644</v>
       </c>
       <c r="B5" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608525</v>
+        <v>608781</v>
       </c>
       <c r="R5" t="n">
-        <v>7020802</v>
+        <v>7020679</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126237644</v>
+        <v>126237641</v>
       </c>
       <c r="B6" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608781</v>
+        <v>608525</v>
       </c>
       <c r="R6" t="n">
-        <v>7020679</v>
+        <v>7020802</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1163,7 +1163,7 @@
         <v>126237648</v>
       </c>
       <c r="B7" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126237647</v>
       </c>
       <c r="B8" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126237646</v>
       </c>
       <c r="B9" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126237642</v>
       </c>
       <c r="B10" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 25919-2025 artfynd.xlsx
+++ b/artfynd/A 25919-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126222584</v>
       </c>
       <c r="B2" t="n">
-        <v>101435</v>
+        <v>101438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126237645</v>
       </c>
       <c r="B3" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126237643</v>
+        <v>126237644</v>
       </c>
       <c r="B4" t="n">
-        <v>91260</v>
+        <v>100441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608473</v>
+        <v>608781</v>
       </c>
       <c r="R4" t="n">
-        <v>7020757</v>
+        <v>7020679</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126237644</v>
+        <v>126237641</v>
       </c>
       <c r="B5" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608781</v>
+        <v>608525</v>
       </c>
       <c r="R5" t="n">
-        <v>7020679</v>
+        <v>7020802</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126237641</v>
+        <v>126237643</v>
       </c>
       <c r="B6" t="n">
-        <v>100438</v>
+        <v>91260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608525</v>
+        <v>608473</v>
       </c>
       <c r="R6" t="n">
-        <v>7020802</v>
+        <v>7020757</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1163,7 +1163,7 @@
         <v>126237648</v>
       </c>
       <c r="B7" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126237647</v>
       </c>
       <c r="B8" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126237646</v>
       </c>
       <c r="B9" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126237642</v>
       </c>
       <c r="B10" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 25919-2025 artfynd.xlsx
+++ b/artfynd/A 25919-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126237644</v>
+        <v>126237643</v>
       </c>
       <c r="B4" t="n">
-        <v>100441</v>
+        <v>91260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608781</v>
+        <v>608473</v>
       </c>
       <c r="R4" t="n">
-        <v>7020679</v>
+        <v>7020757</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126237641</v>
+        <v>126237644</v>
       </c>
       <c r="B5" t="n">
         <v>100441</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608525</v>
+        <v>608781</v>
       </c>
       <c r="R5" t="n">
-        <v>7020802</v>
+        <v>7020679</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126237643</v>
+        <v>126237641</v>
       </c>
       <c r="B6" t="n">
-        <v>91260</v>
+        <v>100441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608473</v>
+        <v>608525</v>
       </c>
       <c r="R6" t="n">
-        <v>7020757</v>
+        <v>7020802</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 25919-2025 artfynd.xlsx
+++ b/artfynd/A 25919-2025 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126237644</v>
+        <v>126237641</v>
       </c>
       <c r="B5" t="n">
         <v>100441</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608781</v>
+        <v>608525</v>
       </c>
       <c r="R5" t="n">
-        <v>7020679</v>
+        <v>7020802</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126237641</v>
+        <v>126237644</v>
       </c>
       <c r="B6" t="n">
         <v>100441</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608525</v>
+        <v>608781</v>
       </c>
       <c r="R6" t="n">
-        <v>7020802</v>
+        <v>7020679</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 25919-2025 artfynd.xlsx
+++ b/artfynd/A 25919-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126222584</v>
       </c>
       <c r="B2" t="n">
-        <v>101438</v>
+        <v>101447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126237645</v>
       </c>
       <c r="B3" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126237643</v>
       </c>
       <c r="B4" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126237641</v>
       </c>
       <c r="B5" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126237644</v>
       </c>
       <c r="B6" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126237648</v>
       </c>
       <c r="B7" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126237647</v>
       </c>
       <c r="B8" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126237646</v>
       </c>
       <c r="B9" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126237642</v>
       </c>
       <c r="B10" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 25919-2025 artfynd.xlsx
+++ b/artfynd/A 25919-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126237643</v>
+        <v>126237641</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>100450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608473</v>
+        <v>608525</v>
       </c>
       <c r="R4" t="n">
-        <v>7020757</v>
+        <v>7020802</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126237641</v>
+        <v>126237644</v>
       </c>
       <c r="B5" t="n">
         <v>100450</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608525</v>
+        <v>608781</v>
       </c>
       <c r="R5" t="n">
-        <v>7020802</v>
+        <v>7020679</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126237644</v>
+        <v>126237643</v>
       </c>
       <c r="B6" t="n">
-        <v>100450</v>
+        <v>91263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608781</v>
+        <v>608473</v>
       </c>
       <c r="R6" t="n">
-        <v>7020679</v>
+        <v>7020757</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 25919-2025 artfynd.xlsx
+++ b/artfynd/A 25919-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126237641</v>
+        <v>126237643</v>
       </c>
       <c r="B4" t="n">
-        <v>100450</v>
+        <v>91263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608525</v>
+        <v>608473</v>
       </c>
       <c r="R4" t="n">
-        <v>7020802</v>
+        <v>7020757</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126237644</v>
+        <v>126237641</v>
       </c>
       <c r="B5" t="n">
         <v>100450</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608781</v>
+        <v>608525</v>
       </c>
       <c r="R5" t="n">
-        <v>7020679</v>
+        <v>7020802</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126237643</v>
+        <v>126237644</v>
       </c>
       <c r="B6" t="n">
-        <v>91263</v>
+        <v>100450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608473</v>
+        <v>608781</v>
       </c>
       <c r="R6" t="n">
-        <v>7020757</v>
+        <v>7020679</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 25919-2025 artfynd.xlsx
+++ b/artfynd/A 25919-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126222584</v>
+        <v>105164648</v>
       </c>
       <c r="B2" t="n">
-        <v>101447</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608754</v>
+        <v>609100</v>
       </c>
       <c r="R2" t="n">
-        <v>7020692</v>
+        <v>7020577</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,60 +760,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126237645</v>
+        <v>126222584</v>
       </c>
       <c r="B3" t="n">
-        <v>100450</v>
+        <v>102241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Yttersel, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608781</v>
+        <v>608754</v>
       </c>
       <c r="R3" t="n">
-        <v>7020690</v>
+        <v>7020692</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,32 +873,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126237643</v>
+        <v>126237640</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>101228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608473</v>
+        <v>608560</v>
       </c>
       <c r="R4" t="n">
-        <v>7020757</v>
+        <v>7020816</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,7 +973,7 @@
         <v>126237641</v>
       </c>
       <c r="B5" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126237644</v>
+        <v>126237642</v>
       </c>
       <c r="B6" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608781</v>
+        <v>608424</v>
       </c>
       <c r="R6" t="n">
-        <v>7020679</v>
+        <v>7020779</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1128,12 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126237648</v>
+        <v>126237644</v>
       </c>
       <c r="B7" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608849</v>
+        <v>608781</v>
       </c>
       <c r="R7" t="n">
-        <v>7020693</v>
+        <v>7020679</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126237647</v>
+        <v>126237645</v>
       </c>
       <c r="B8" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608837</v>
+        <v>608781</v>
       </c>
       <c r="R8" t="n">
-        <v>7020681</v>
+        <v>7020690</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1357,7 +1361,7 @@
         <v>126237646</v>
       </c>
       <c r="B9" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1455,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126237642</v>
+        <v>126237647</v>
       </c>
       <c r="B10" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608424</v>
+        <v>608837</v>
       </c>
       <c r="R10" t="n">
-        <v>7020779</v>
+        <v>7020681</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1516,12 +1520,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1545,6 +1549,103 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126237648</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>608849</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7020693</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25919-2025 artfynd.xlsx
+++ b/artfynd/A 25919-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126222584</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126237640</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126237641</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126237642</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126237644</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126237645</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126237646</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164648</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126237647</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,8 +1696,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126237648</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>